--- a/results/0916-all/长白山地林农区/tech_selected_summary.xlsx
+++ b/results/0916-all/长白山地林农区/tech_selected_summary.xlsx
@@ -130,124 +130,124 @@
     <t>长白朝鲜族自治县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 0.00</t>
+    <t>0.00</t>
   </si>
   <si>
     <t>4R(Right place)_rice</t>
@@ -256,19 +256,19 @@
     <t>4R(Right rate)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 258717.98</t>
+    <t>258717.98</t>
   </si>
   <si>
     <t>cover crop (mix)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 168047.73</t>
+    <t>168047.73</t>
   </si>
   <si>
     <t>EEF(NI)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 23350813.31</t>
+    <t>23350813.31</t>
   </si>
   <si>
     <t>EEF(NI)_vegetable</t>
@@ -292,34 +292,34 @@
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 8391533.79</t>
+    <t>8391533.79</t>
   </si>
   <si>
     <t>surface crust cover_pig</t>
   </si>
   <si>
-    <t>总经济成本: 649619.04</t>
+    <t>649619.04</t>
   </si>
   <si>
     <t>Yucca extract_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 12478.50</t>
+    <t>12478.50</t>
   </si>
   <si>
     <t>EEF(NI)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 99950.40</t>
-  </si>
-  <si>
-    <t>总经济成本: 16771.30</t>
+    <t>99950.40</t>
+  </si>
+  <si>
+    <t>16771.30</t>
   </si>
   <si>
     <t>EEF(NI)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 6125603.43</t>
+    <t>6125603.43</t>
   </si>
   <si>
     <t>Increasing byproduct_pig</t>
@@ -394,22 +394,22 @@
     <t>4R(Right place)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 102183316.84</t>
-  </si>
-  <si>
-    <t>总经济成本: 10516480.50</t>
-  </si>
-  <si>
-    <t>总经济成本: 8298826.51</t>
-  </si>
-  <si>
-    <t>总经济成本: 20869768.87</t>
-  </si>
-  <si>
-    <t>总经济成本: 14026198.91</t>
-  </si>
-  <si>
-    <t>总经济成本: 1161687.39</t>
+    <t>102183316.84</t>
+  </si>
+  <si>
+    <t>10516480.50</t>
+  </si>
+  <si>
+    <t>8298826.51</t>
+  </si>
+  <si>
+    <t>20869768.87</t>
+  </si>
+  <si>
+    <t>14026198.91</t>
+  </si>
+  <si>
+    <t>1161687.39</t>
   </si>
 </sst>
 </file>
